--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/4_five_bus_radial_grid_1ph_yyn_MP_pf_sc_results_0_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/4_five_bus_radial_grid_1ph_yyn_MP_pf_sc_results_0_bus.xlsx
@@ -68,19 +68,19 @@
     <t>pf_va_degree</t>
   </si>
   <si>
-    <t>Bus_0</t>
-  </si>
-  <si>
     <t>Bus_1</t>
-  </si>
-  <si>
-    <t>Bus_2</t>
   </si>
   <si>
     <t>Bus_3</t>
   </si>
   <si>
     <t>Bus_4</t>
+  </si>
+  <si>
+    <t>Bus_0</t>
+  </si>
+  <si>
+    <t>Bus_2</t>
   </si>
   <si>
     <t>pf_ikss_a_ka</t>
@@ -526,22 +526,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>5.248639108480242</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1000.000056712887</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1.324394473835045</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>13.24394453564036</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>84.28940677566905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -595,22 +595,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>5.248639108480242</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1000.000056712887</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1.324394473835045</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>13.24394453564036</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>84.28940677566905</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -707,7 +707,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -766,7 +766,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -825,7 +825,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -943,7 +943,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1071,7 +1071,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1189,7 +1189,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1248,7 +1248,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1307,7 +1307,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1435,7 +1435,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1553,7 +1553,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1612,7 +1612,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1917,7 +1917,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2281,7 +2281,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2399,7 +2399,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2527,7 +2527,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2645,7 +2645,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -2704,7 +2704,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2763,7 +2763,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2891,7 +2891,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3127,7 +3127,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>5.248639108051611</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3382,7 +3382,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3444,7 +3444,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3506,7 +3506,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3640,7 +3640,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>5.248639108051611</v>
@@ -3702,7 +3702,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3764,7 +3764,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3826,7 +3826,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4022,7 +4022,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.617960381730407</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4146,7 +4146,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4365,7 +4365,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>5.248639108480242</v>
@@ -4388,7 +4388,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4457,7 +4457,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4552,7 +4552,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.617960381730407</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4676,7 +4676,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4738,7 +4738,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4934,7 +4934,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>4.198911195465507</v>
@@ -4996,7 +4996,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5058,7 +5058,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5182,7 +5182,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>4.198911195465507</v>
@@ -5378,7 +5378,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5440,7 +5440,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5502,7 +5502,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5564,7 +5564,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -5698,7 +5698,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.012913138226506</v>
@@ -5760,7 +5760,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5822,7 +5822,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5884,7 +5884,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6080,7 +6080,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.012913138226506</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6204,7 +6204,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6266,7 +6266,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6328,7 +6328,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6462,7 +6462,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6524,7 +6524,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6648,7 +6648,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6710,7 +6710,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6844,7 +6844,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6906,7 +6906,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6968,7 +6968,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7030,7 +7030,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7092,7 +7092,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7226,7 +7226,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -7288,7 +7288,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7350,7 +7350,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7412,7 +7412,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7474,7 +7474,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7608,7 +7608,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -7670,7 +7670,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7732,7 +7732,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7794,7 +7794,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7856,7 +7856,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7990,7 +7990,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -8052,7 +8052,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8114,7 +8114,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8176,7 +8176,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8238,7 +8238,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -8333,7 +8333,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.617960382498488</v>
@@ -8356,7 +8356,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8379,7 +8379,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8402,7 +8402,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8425,7 +8425,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -8520,7 +8520,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -8582,7 +8582,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8644,7 +8644,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8706,7 +8706,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8768,7 +8768,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -8902,7 +8902,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -8964,7 +8964,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9026,7 +9026,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9088,7 +9088,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9150,7 +9150,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9284,7 +9284,7 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -9346,7 +9346,7 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9408,7 +9408,7 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9470,7 +9470,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9532,7 +9532,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9627,7 +9627,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.617960382498489</v>
@@ -9650,7 +9650,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9673,7 +9673,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9696,7 +9696,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9719,7 +9719,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9775,7 +9775,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>4.198911195753389</v>
@@ -9798,7 +9798,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9821,7 +9821,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9844,7 +9844,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9867,7 +9867,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9923,7 +9923,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>4.198911195753389</v>
@@ -9946,7 +9946,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -9969,7 +9969,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -9992,7 +9992,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -10015,7 +10015,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -10071,7 +10071,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.012913138782225</v>
@@ -10094,7 +10094,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -10117,7 +10117,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -10140,7 +10140,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -10163,7 +10163,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -10219,7 +10219,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>3.012913138782225</v>
@@ -10242,7 +10242,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -10265,7 +10265,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -10288,7 +10288,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -10311,7 +10311,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -10403,7 +10403,7 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -10462,7 +10462,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -10521,7 +10521,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -10580,7 +10580,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -10639,7 +10639,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0</v>
